--- a/outputs/daily/hr_rankings_2026-07-09_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-09_full.xlsx
@@ -1044,7 +1044,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>64.3</v>
+        <v>64.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>82.7</v>
+        <v>87</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1713,22 +1713,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -11604,7 +11604,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>78</v>
       </c>
       <c r="U41" t="n">
-        <v>79.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>50</v>
       </c>
       <c r="U64" t="n">
-        <v>42.3</v>
+        <v>40.7</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -18140,7 +18140,7 @@
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 1 HR</t>
+          <t>Last 7 games: 7/26, 1 HR</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
@@ -18271,27 +18271,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>663616</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Trevor Larnach</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-09T17:40:00Z</t>
+          <t>2026-07-09T17:10:00Z</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -18306,12 +18306,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -18334,17 +18334,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>29.4</v>
+        <v>50.3</v>
       </c>
       <c r="Q65" t="n">
-        <v>59.5</v>
+        <v>30.2</v>
       </c>
       <c r="R65" t="n">
-        <v>39.6</v>
+        <v>41.1</v>
       </c>
       <c r="S65" t="n">
         <v>93.2</v>
@@ -18353,7 +18353,7 @@
         <v>80</v>
       </c>
       <c r="U65" t="n">
-        <v>37.8</v>
+        <v>34.4</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -18420,12 +18420,12 @@
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 1 HR</t>
+          <t>Last 7 games: 5/22, 1 HR</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.4% barrel, 18.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.7% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
@@ -18435,112 +18435,112 @@
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>46.26</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>88.31</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>99.2939</t>
+          <t>100.8754</t>
         </is>
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>0.4037</t>
+          <t>0.4609</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.2101</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr">
         <is>
-          <t>0.3334</t>
+          <t>0.356</t>
         </is>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>71.99</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>41.36</t>
+          <t>43.81</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>25.31</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.1961</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="BD65" t="inlineStr">
         <is>
-          <t>0.4316</t>
+          <t>0.3652</t>
         </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
-          <t>0.1894</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="BG65" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI65" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ65" t="inlineStr"/>
@@ -18551,27 +18551,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>663757</t>
+          <t>800050</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-09T17:10:00Z</t>
+          <t>2026-07-09T17:40:00Z</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -18581,17 +18581,17 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Bailey Ober</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>641927</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -18614,26 +18614,26 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>50.3</v>
+        <v>29.9</v>
       </c>
       <c r="Q66" t="n">
-        <v>30.2</v>
+        <v>50.6</v>
       </c>
       <c r="R66" t="n">
-        <v>41.1</v>
+        <v>39.6</v>
       </c>
       <c r="S66" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T66" t="n">
         <v>80</v>
       </c>
       <c r="U66" t="n">
-        <v>34.4</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -18668,7 +18668,7 @@
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr"/>
@@ -18685,142 +18685,142 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.7% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.1% barrel, 17.4 HR allowed</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
-          <t>100.8754</t>
+          <t>101.3496</t>
         </is>
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>0.4609</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>0.2101</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>0.337</t>
         </is>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>43.81</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>0.1961</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>10.13</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="BD66" t="inlineStr">
         <is>
-          <t>0.3652</t>
+          <t>0.4508</t>
         </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.2049</t>
         </is>
       </c>
       <c r="BF66" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="BG66" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI66" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ66" t="inlineStr"/>
@@ -18831,24 +18831,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>700932</t>
+          <t>663616</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kyle Manzardo</t>
+          <t>Trevor Larnach</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>2026-07-09T17:40:00Z</t>
@@ -18861,17 +18861,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Bailey Ober</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>641927</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -18880,7 +18880,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -18894,26 +18894,26 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>40.4</v>
+        <v>29.4</v>
       </c>
       <c r="Q67" t="n">
-        <v>50.6</v>
+        <v>59.5</v>
       </c>
       <c r="R67" t="n">
         <v>39.6</v>
       </c>
       <c r="S67" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T67" t="n">
         <v>80</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -18965,127 +18965,127 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/20, 0 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.1% barrel, 17.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.4% barrel, 18.1 HR allowed</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>37.93</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>88.31</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>99.1104</t>
+          <t>99.2939</t>
         </is>
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>0.3947</t>
+          <t>0.4037</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.1439</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr">
         <is>
-          <t>0.3101</t>
+          <t>0.3334</t>
         </is>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>71.99</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>20.96</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.36</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>25.31</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1519</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>10.13</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD67" t="inlineStr">
         <is>
-          <t>0.4508</t>
+          <t>0.4316</t>
         </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
-          <t>0.2049</t>
+          <t>0.1894</t>
         </is>
       </c>
       <c r="BF67" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="BG67" t="inlineStr">
@@ -19111,12 +19111,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>672356</t>
+          <t>700932</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Gabriel Arias</t>
+          <t>Kyle Manzardo</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -19141,7 +19141,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -19160,7 +19160,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>51.5</v>
+        <v>51.9</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -19174,11 +19174,11 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>46.5</v>
+        <v>40.4</v>
       </c>
       <c r="Q68" t="n">
         <v>50.6</v>
@@ -19187,13 +19187,13 @@
         <v>39.6</v>
       </c>
       <c r="S68" t="n">
-        <v>76.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T68" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U68" t="n">
-        <v>58.7</v>
+        <v>0</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -19245,27 +19245,27 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 1/20, 0 HR</t>
         </is>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.1% barrel, 17.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.1% barrel, 17.4 HR allowed</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
@@ -19275,67 +19275,67 @@
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>11.16</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>48.76</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>103.0682</t>
+          <t>99.1104</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>0.3927</t>
+          <t>0.3947</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>0.1752</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr">
         <is>
-          <t>0.2839</t>
+          <t>0.3101</t>
         </is>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>74.61</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>0.1661</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
@@ -19391,47 +19391,47 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>592663</t>
+          <t>672356</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Gabriel Arias</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-09T23:10:00Z</t>
+          <t>2026-07-09T17:40:00Z</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>Bailey Ober</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>663903</t>
+          <t>641927</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -19440,7 +19440,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -19454,62 +19454,58 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Projected Lineup, Good Environment</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>30.9</v>
+        <v>46.5</v>
       </c>
       <c r="Q69" t="n">
-        <v>58.6</v>
+        <v>50.6</v>
       </c>
       <c r="R69" t="n">
-        <v>79.8</v>
+        <v>39.6</v>
       </c>
       <c r="S69" t="n">
-        <v>59.8</v>
+        <v>76.2</v>
       </c>
       <c r="T69" t="n">
         <v>50</v>
       </c>
       <c r="U69" t="n">
-        <v>44.8</v>
+        <v>58.7</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19534,7 +19530,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -19549,122 +19545,122 @@
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.1% barrel, 17.4 HR allowed</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>11.16</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>48.76</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>89.37</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>99.4447</t>
+          <t>103.0682</t>
         </is>
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>0.3865</t>
+          <t>0.3927</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>0.1426</t>
+          <t>0.1752</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
-          <t>0.3125</t>
+          <t>0.2839</t>
         </is>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>72.77</t>
+          <t>74.61</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>30.71</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.1661</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>10.13</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>90.86</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="BD69" t="inlineStr">
         <is>
-          <t>0.4608</t>
+          <t>0.4508</t>
         </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
-          <t>0.1982</t>
+          <t>0.2049</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI69" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ69" t="inlineStr"/>
@@ -19675,27 +19671,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>670042</t>
+          <t>592663</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Luke Raley</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-09T22:40:00Z</t>
+          <t>2026-07-09T23:10:00Z</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -19705,17 +19701,17 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Janson Junk</t>
+          <t>Brady Singer</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>676083</t>
+          <t>663903</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -19724,7 +19720,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>51.1</v>
+        <v>51.3</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -19738,58 +19734,62 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Good Environment</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>54.2</v>
+        <v>30.9</v>
       </c>
       <c r="Q70" t="n">
-        <v>41.6</v>
+        <v>58.6</v>
       </c>
       <c r="R70" t="n">
-        <v>35</v>
+        <v>79.8</v>
       </c>
       <c r="S70" t="n">
-        <v>76.2</v>
+        <v>59.8</v>
       </c>
       <c r="T70" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U70" t="n">
-        <v>1.6</v>
+        <v>44.8</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19809,7 +19809,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr">
@@ -19819,17 +19819,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
@@ -19839,112 +19839,112 @@
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>45.31</t>
+          <t>40.18</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>89.37</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>101.9314</t>
+          <t>99.4447</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>0.4504</t>
+          <t>0.3865</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1426</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>0.3344</t>
+          <t>0.3125</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>74.78</t>
+          <t>72.77</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>50.34</t>
+          <t>30.71</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>47.27</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>0.1972</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>90.86</t>
         </is>
       </c>
       <c r="BD70" t="inlineStr">
         <is>
-          <t>0.4236</t>
+          <t>0.4608</t>
         </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
-          <t>0.1606</t>
+          <t>0.1982</t>
         </is>
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG70" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BI70" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ70" t="inlineStr"/>
@@ -19955,47 +19955,47 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>670042</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Luke Raley</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-09T16:35:00Z</t>
+          <t>2026-07-09T22:40:00Z</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Janson Junk</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>676083</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -20018,26 +20018,26 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>48.3</v>
+        <v>54.2</v>
       </c>
       <c r="Q71" t="n">
-        <v>43.5</v>
+        <v>41.6</v>
       </c>
       <c r="R71" t="n">
-        <v>63.3</v>
+        <v>35</v>
       </c>
       <c r="S71" t="n">
-        <v>64.3</v>
+        <v>76.2</v>
       </c>
       <c r="T71" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U71" t="n">
-        <v>31.6</v>
+        <v>1.6</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -20089,27 +20089,27 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 1 HR</t>
+          <t>Last 7 games: 3/23, 0 HR</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.5% barrel, 14.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
@@ -20119,112 +20119,112 @@
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>45.31</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>102.2808</t>
+          <t>101.9314</t>
         </is>
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>0.3992</t>
+          <t>0.4504</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>0.3344</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>75.76</t>
+          <t>74.78</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>58.47</t>
+          <t>50.34</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>47.27</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>31.43</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>0.1393</t>
+          <t>0.1972</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>42.54</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="BD71" t="inlineStr">
         <is>
-          <t>0.4461</t>
+          <t>0.4236</t>
         </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.1606</t>
         </is>
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="BG71" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI71" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ71" t="inlineStr"/>
@@ -20235,47 +20235,47 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-09T23:45:00Z</t>
+          <t>2026-07-09T16:35:00Z</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>669467</t>
+          <t>656605</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -20298,62 +20298,58 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>38.1</v>
+        <v>48.3</v>
       </c>
       <c r="Q72" t="n">
-        <v>28.5</v>
+        <v>43.5</v>
       </c>
       <c r="R72" t="n">
-        <v>65.59999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="S72" t="n">
-        <v>92.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T72" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U72" t="n">
-        <v>33.6</v>
+        <v>31.6</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -20373,27 +20369,27 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Contact streak: 11/32 over last 7 games</t>
+          <t>Last 7 games: 5/24, 1 HR</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.5% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
@@ -20403,112 +20399,112 @@
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>44.53</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>90.82</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>100.6447</t>
+          <t>102.2808</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.3992</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>0.1768</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.302</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>75.76</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>58.47</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>40.57</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>31.43</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>0.1757</t>
+          <t>0.1393</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>36.19</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>87.87</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="BD72" t="inlineStr">
         <is>
-          <t>0.3824</t>
+          <t>0.4461</t>
         </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
-          <t>0.1384</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="BF72" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="BG72" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI72" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ72" t="inlineStr"/>
@@ -20519,32 +20515,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>800050</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-09T17:40:00Z</t>
+          <t>2026-07-09T23:45:00Z</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -20554,12 +20550,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Bailey Ober</t>
+          <t>Andre Pallante</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>641927</t>
+          <t>669467</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -20568,7 +20564,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -20582,61 +20578,65 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>29.9</v>
+        <v>38.1</v>
       </c>
       <c r="Q73" t="n">
-        <v>50.6</v>
+        <v>28.5</v>
       </c>
       <c r="R73" t="n">
-        <v>39.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S73" t="n">
-        <v>96.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T73" t="n">
         <v>80</v>
       </c>
       <c r="U73" t="n">
-        <v>44.8</v>
+        <v>33.6</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr"/>
@@ -20653,142 +20653,142 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 1 HR</t>
+          <t>Contact streak: 11/32 over last 7 games</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.1% barrel, 17.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>44.53</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.82</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>101.3496</t>
+          <t>100.6447</t>
         </is>
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1768</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>27.23</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.1757</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>10.13</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>36.19</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>87.87</t>
         </is>
       </c>
       <c r="BD73" t="inlineStr">
         <is>
-          <t>0.4508</t>
+          <t>0.3824</t>
         </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
-          <t>0.2049</t>
+          <t>0.1384</t>
         </is>
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="BG73" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI73" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ73" t="inlineStr"/>
@@ -21079,27 +21079,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>678882</t>
+          <t>701807</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Carson Benge</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-09T18:10:00Z</t>
+          <t>2026-07-09T17:10:00Z</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -21109,22 +21109,22 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -21146,22 +21146,22 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>21.8</v>
+        <v>36.8</v>
       </c>
       <c r="Q75" t="n">
-        <v>40.3</v>
+        <v>34.3</v>
       </c>
       <c r="R75" t="n">
-        <v>66.59999999999999</v>
+        <v>44.3</v>
       </c>
       <c r="S75" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T75" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U75" t="n">
-        <v>50.3</v>
+        <v>58</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
@@ -21196,7 +21196,7 @@
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr"/>
@@ -21218,7 +21218,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -21228,12 +21228,12 @@
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Contact streak: 10/30 over last 7 games</t>
+          <t>Contact streak: 10/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.6% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
@@ -21243,112 +21243,112 @@
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>86.83</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>97.877</t>
+          <t>100.1929</t>
         </is>
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>0.3747</t>
+          <t>0.458</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>0.1299</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr">
         <is>
-          <t>0.2938</t>
+          <t>0.353</t>
         </is>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>70.23</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>0.1594</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>35.86</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.99</t>
         </is>
       </c>
       <c r="BD75" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.4123</t>
         </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>0.1612</t>
         </is>
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>26.78</t>
         </is>
       </c>
       <c r="BG75" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI75" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ75" t="inlineStr"/>
@@ -21359,47 +21359,47 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>679822</t>
+          <t>678882</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Justin Foscue</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-10T00:05:00Z</t>
+          <t>2026-07-09T18:10:00Z</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>672282</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -21422,65 +21422,61 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>45.8</v>
+        <v>21.8</v>
       </c>
       <c r="Q76" t="n">
-        <v>33.3</v>
+        <v>40.3</v>
       </c>
       <c r="R76" t="n">
-        <v>27.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="S76" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T76" t="n">
         <v>78</v>
       </c>
       <c r="U76" t="n">
-        <v>73.90000000000001</v>
+        <v>50.3</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr"/>
@@ -21497,27 +21493,27 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 10/30 over last 7 games</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 8.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
@@ -21527,104 +21523,112 @@
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>52.07</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>90.55</t>
+          <t>86.83</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>100.0572</t>
+          <t>97.877</t>
         </is>
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>0.4295</t>
+          <t>0.3747</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>0.1929</t>
+          <t>0.1299</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr">
         <is>
-          <t>0.3108</t>
+          <t>0.2938</t>
         </is>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>70.23</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>43.21</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>33.48</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>0.2069</t>
+          <t>0.1594</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>38.74</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>89.68</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="BD76" t="inlineStr">
         <is>
-          <t>0.3469</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
-          <t>0.1271</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>27.29</t>
-        </is>
-      </c>
-      <c r="BG76" t="inlineStr"/>
-      <c r="BH76" t="inlineStr"/>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="BG76" t="inlineStr">
+        <is>
+          <t>Out To LF</t>
+        </is>
+      </c>
+      <c r="BH76" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="BI76" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ76" t="inlineStr"/>
@@ -21635,56 +21639,56 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>701807</t>
+          <t>679822</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Carson Benge</t>
+          <t>Justin Foscue</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-09T17:10:00Z</t>
+          <t>2026-07-10T00:05:00Z</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Reid Detmers</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>672282</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -21698,61 +21702,65 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>36.8</v>
+        <v>45.8</v>
       </c>
       <c r="Q77" t="n">
-        <v>34.3</v>
+        <v>33.3</v>
       </c>
       <c r="R77" t="n">
-        <v>44.3</v>
+        <v>27.6</v>
       </c>
       <c r="S77" t="n">
-        <v>94.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T77" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U77" t="n">
-        <v>54.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr"/>
@@ -21769,27 +21777,27 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.6% barrel, 13.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 8.1 HR allowed</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -21799,112 +21807,104 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>52.07</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>100.1929</t>
+          <t>100.0572</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>0.458</t>
+          <t>0.4295</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.1929</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>0.3108</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>43.21</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>33.48</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.2069</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>35.86</t>
+          <t>38.74</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>87.99</t>
+          <t>89.68</t>
         </is>
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>0.4123</t>
+          <t>0.3469</t>
         </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
-          <t>0.1612</t>
+          <t>0.1271</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>26.78</t>
-        </is>
-      </c>
-      <c r="BG77" t="inlineStr">
-        <is>
-          <t>In From CF</t>
-        </is>
-      </c>
-      <c r="BH77" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
+          <t>27.29</t>
+        </is>
+      </c>
+      <c r="BG77" t="inlineStr"/>
+      <c r="BH77" t="inlineStr"/>
       <c r="BI77" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ77" t="inlineStr"/>
@@ -26189,7 +26189,7 @@
         <v>78</v>
       </c>
       <c r="U93" t="n">
-        <v>34.4</v>
+        <v>32.9</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
@@ -26256,7 +26256,7 @@
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 1 HR</t>
+          <t>Last 7 games: 5/23, 1 HR</t>
         </is>
       </c>
       <c r="AL93" t="inlineStr">
@@ -26688,7 +26688,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -31424,7 +31424,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -32795,22 +32795,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>666182</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bo Bichette</t>
+          <t>Jazz Chisholm Jr.</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -32825,17 +32825,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -32858,26 +32858,26 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>35.8</v>
+        <v>42.7</v>
       </c>
       <c r="Q117" t="n">
-        <v>34.3</v>
+        <v>30.2</v>
       </c>
       <c r="R117" t="n">
-        <v>44.3</v>
+        <v>41.1</v>
       </c>
       <c r="S117" t="n">
-        <v>96.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T117" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U117" t="n">
-        <v>32</v>
+        <v>17.7</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -32891,7 +32891,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
@@ -32929,12 +32929,12 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
@@ -32944,12 +32944,12 @@
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Contact streak: 10/30 over last 7 games</t>
+          <t>Last 7 games: 5/21, 0 HR</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 13.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.7% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
@@ -32959,112 +32959,112 @@
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>90.51</t>
+          <t>90.19</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>101.4865</t>
+          <t>100.405</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
         <is>
-          <t>0.4429</t>
+          <t>0.3977</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>0.1552</t>
+          <t>0.1826</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>0.3376</t>
+          <t>0.3082</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>73.34</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>34.48</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>53.24</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>29.77</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1886</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>35.86</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>87.99</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="BD117" t="inlineStr">
         <is>
-          <t>0.4123</t>
+          <t>0.3652</t>
         </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
-          <t>0.1612</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="BG117" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI117" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ117" t="inlineStr"/>
@@ -33075,27 +33075,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>642086</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jazz Chisholm Jr.</t>
+          <t>Dominic Smith</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-09T17:10:00Z</t>
+          <t>2026-07-09T16:35:00Z</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -33110,12 +33110,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>656605</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -33124,7 +33124,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
@@ -33138,17 +33138,17 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P118" t="n">
-        <v>42.7</v>
+        <v>23.6</v>
       </c>
       <c r="Q118" t="n">
-        <v>30.2</v>
+        <v>43.5</v>
       </c>
       <c r="R118" t="n">
-        <v>41.1</v>
+        <v>63.3</v>
       </c>
       <c r="S118" t="n">
         <v>76.2</v>
@@ -33157,7 +33157,7 @@
         <v>80</v>
       </c>
       <c r="U118" t="n">
-        <v>17.7</v>
+        <v>12</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
@@ -33224,12 +33224,12 @@
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL118" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.7% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
@@ -33239,112 +33239,112 @@
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>35.15</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>90.19</t>
+          <t>87.63</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>100.405</t>
+          <t>98.233</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
         <is>
-          <t>0.3977</t>
+          <t>0.4036</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>0.1826</t>
+          <t>0.1443</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>0.3082</t>
+          <t>0.3116</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>73.34</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>34.48</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>53.24</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>0.1886</t>
+          <t>0.1302</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="BD118" t="inlineStr">
         <is>
-          <t>0.3652</t>
+          <t>0.4461</t>
         </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="BF118" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="BG118" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI118" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ118" t="inlineStr"/>
@@ -33355,47 +33355,47 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>642086</t>
+          <t>666182</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dominic Smith</t>
+          <t>Bo Bichette</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-09T16:35:00Z</t>
+          <t>2026-07-09T17:10:00Z</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -33418,26 +33418,26 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P119" t="n">
-        <v>23.6</v>
+        <v>35.8</v>
       </c>
       <c r="Q119" t="n">
-        <v>43.5</v>
+        <v>34.3</v>
       </c>
       <c r="R119" t="n">
-        <v>63.3</v>
+        <v>44.3</v>
       </c>
       <c r="S119" t="n">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T119" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U119" t="n">
-        <v>12</v>
+        <v>30.4</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -33489,12 +33489,12 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
@@ -33504,12 +33504,12 @@
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 10/31 over last 7 games</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 14.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
@@ -33519,112 +33519,112 @@
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>87.63</t>
+          <t>90.51</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>98.233</t>
+          <t>101.4865</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>0.4036</t>
+          <t>0.4429</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>0.1443</t>
+          <t>0.1552</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>0.3116</t>
+          <t>0.3376</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>0.1302</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>42.54</t>
+          <t>35.86</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>87.99</t>
         </is>
       </c>
       <c r="BD119" t="inlineStr">
         <is>
-          <t>0.4461</t>
+          <t>0.4123</t>
         </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.1612</t>
         </is>
       </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>26.78</t>
         </is>
       </c>
       <c r="BG119" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI119" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ119" t="inlineStr"/>
@@ -34326,7 +34326,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
@@ -34336,7 +34336,7 @@
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/26, 0 HR</t>
+          <t>Last 7 games: 3/27, 0 HR</t>
         </is>
       </c>
       <c r="AL122" t="inlineStr">
@@ -34829,7 +34829,7 @@
         <v>75</v>
       </c>
       <c r="U124" t="n">
-        <v>61.5</v>
+        <v>59.6</v>
       </c>
       <c r="V124" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
@@ -40304,7 +40304,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -41955,52 +41955,52 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>702222</t>
+          <t>702332</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Justin Crawford</t>
+          <t>Caleb Durbin</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-07-09T23:10:00Z</t>
+          <t>2026-07-09T18:10:00Z</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>663903</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L150" t="n">
@@ -42018,65 +42018,61 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Projected Lineup, Good Environment, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P150" t="n">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="Q150" t="n">
-        <v>58.6</v>
+        <v>40.3</v>
       </c>
       <c r="R150" t="n">
-        <v>79.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="S150" t="n">
-        <v>40.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T150" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U150" t="n">
-        <v>32</v>
+        <v>44.8</v>
       </c>
       <c r="V150" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr"/>
@@ -42093,27 +42089,27 @@
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL150" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.7% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM150" t="inlineStr">
@@ -42123,97 +42119,97 @@
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>28.51</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>84.92</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>97.5538</t>
+          <t>96.3013</t>
         </is>
       </c>
       <c r="AR150" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.3424</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>0.2938</t>
         </is>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>0.1527</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>90.86</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="BD150" t="inlineStr">
         <is>
-          <t>0.4608</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BE150" t="inlineStr">
         <is>
-          <t>0.1982</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="BF150" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="BG150" t="inlineStr">
@@ -42223,12 +42219,12 @@
       </c>
       <c r="BH150" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI150" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ150" t="inlineStr"/>
@@ -42239,56 +42235,56 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>702222</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Justin Crawford</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-07-09T18:10:00Z</t>
+          <t>2026-07-09T23:10:00Z</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Patrick Sandoval</t>
+          <t>Brady Singer</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>663776</t>
+          <t>663903</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>43.2</v>
+        <v>43.4</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -42302,61 +42298,65 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P151" t="n">
-        <v>21.5</v>
+        <v>8.9</v>
       </c>
       <c r="Q151" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="R151" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="S151" t="n">
         <v>40.2</v>
       </c>
-      <c r="R151" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="S151" t="n">
-        <v>64.3</v>
-      </c>
       <c r="T151" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U151" t="n">
-        <v>14.6</v>
+        <v>32</v>
       </c>
       <c r="V151" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W151" t="inlineStr">
+      <c r="Z151" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr"/>
@@ -42373,12 +42373,12 @@
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
@@ -42388,12 +42388,12 @@
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL151" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.7% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
@@ -42403,57 +42403,57 @@
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>100.2588</t>
+          <t>97.5538</t>
         </is>
       </c>
       <c r="AR151" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.063</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>0.279</t>
         </is>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -42463,15 +42463,39 @@
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>0.157</t>
-        </is>
-      </c>
-      <c r="BA151" t="inlineStr"/>
-      <c r="BB151" t="inlineStr"/>
-      <c r="BC151" t="inlineStr"/>
-      <c r="BD151" t="inlineStr"/>
-      <c r="BE151" t="inlineStr"/>
-      <c r="BF151" t="inlineStr"/>
+          <t>0.092</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>10.73</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>40.77</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>90.86</t>
+        </is>
+      </c>
+      <c r="BD151" t="inlineStr">
+        <is>
+          <t>0.4608</t>
+        </is>
+      </c>
+      <c r="BE151" t="inlineStr">
+        <is>
+          <t>0.1982</t>
+        </is>
+      </c>
+      <c r="BF151" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG151" t="inlineStr">
         <is>
           <t>Out To LF</t>
@@ -42479,12 +42503,12 @@
       </c>
       <c r="BH151" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BI151" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ151" t="inlineStr"/>
@@ -42495,56 +42519,56 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Mauricio Dubón</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-07-09T16:35:00Z</t>
+          <t>2026-07-09T18:10:00Z</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Patrick Sandoval</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>663776</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>42.8</v>
+        <v>43.2</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
@@ -42558,26 +42582,26 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>12.1</v>
+        <v>21.5</v>
       </c>
       <c r="Q152" t="n">
-        <v>43.5</v>
+        <v>40.2</v>
       </c>
       <c r="R152" t="n">
-        <v>63.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="S152" t="n">
-        <v>86.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T152" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U152" t="n">
-        <v>44.8</v>
+        <v>14.6</v>
       </c>
       <c r="V152" t="inlineStr">
         <is>
@@ -42591,7 +42615,7 @@
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
@@ -42612,7 +42636,7 @@
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr"/>
@@ -42629,27 +42653,27 @@
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 1 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.5% barrel, 14.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
@@ -42659,99 +42683,75 @@
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>85.76</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>96.464</t>
+          <t>100.2588</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>0.3765</t>
+          <t>0.351</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>0.1106</t>
+          <t>0.114</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>0.3074</t>
+          <t>0.297</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>68.69</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>0.1413</t>
-        </is>
-      </c>
-      <c r="BA152" t="inlineStr">
-        <is>
-          <t>7.45</t>
-        </is>
-      </c>
-      <c r="BB152" t="inlineStr">
-        <is>
-          <t>42.54</t>
-        </is>
-      </c>
-      <c r="BC152" t="inlineStr">
-        <is>
-          <t>89.47</t>
-        </is>
-      </c>
-      <c r="BD152" t="inlineStr">
-        <is>
-          <t>0.4461</t>
-        </is>
-      </c>
-      <c r="BE152" t="inlineStr">
-        <is>
-          <t>0.164</t>
-        </is>
-      </c>
-      <c r="BF152" t="inlineStr">
-        <is>
-          <t>24.26</t>
-        </is>
-      </c>
+          <t>0.157</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr"/>
+      <c r="BB152" t="inlineStr"/>
+      <c r="BC152" t="inlineStr"/>
+      <c r="BD152" t="inlineStr"/>
+      <c r="BE152" t="inlineStr"/>
+      <c r="BF152" t="inlineStr"/>
       <c r="BG152" t="inlineStr">
         <is>
           <t>Out To LF</t>
@@ -42759,12 +42759,12 @@
       </c>
       <c r="BH152" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI152" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ152" t="inlineStr"/>
@@ -42775,56 +42775,56 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>691720</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-07-10T01:45:00Z</t>
+          <t>2026-07-09T16:35:00Z</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Carson Whisenhunt</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>687931</t>
+          <t>656605</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
@@ -42838,62 +42838,58 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P153" t="n">
-        <v>25.9</v>
+        <v>12.1</v>
       </c>
       <c r="Q153" t="n">
-        <v>31.9</v>
+        <v>43.5</v>
       </c>
       <c r="R153" t="n">
-        <v>19.3</v>
+        <v>63.3</v>
       </c>
       <c r="S153" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T153" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U153" t="n">
-        <v>64.8</v>
+        <v>44.8</v>
       </c>
       <c r="V153" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -42918,129 +42914,137 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/27, 1 HR</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.8% barrel, 1.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.5% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>85.76</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>99.7297</t>
+          <t>96.464</t>
         </is>
       </c>
       <c r="AR153" t="inlineStr">
         <is>
-          <t>0.3649</t>
+          <t>0.3765</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>0.1229</t>
+          <t>0.1106</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr">
         <is>
-          <t>0.3168</t>
+          <t>0.3074</t>
         </is>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>68.69</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>23.22</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>0.1385</t>
+          <t>0.1413</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="BD153" t="inlineStr">
         <is>
-          <t>0.4295</t>
+          <t>0.4461</t>
         </is>
       </c>
       <c r="BE153" t="inlineStr">
         <is>
-          <t>0.1486</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="BG153" t="inlineStr"/>
-      <c r="BH153" t="inlineStr"/>
+          <t>24.26</t>
+        </is>
+      </c>
+      <c r="BG153" t="inlineStr">
+        <is>
+          <t>Out To LF</t>
+        </is>
+      </c>
+      <c r="BH153" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
       <c r="BI153" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ153" t="inlineStr"/>
@@ -43051,27 +43055,27 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>641680</t>
+          <t>691720</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-07-09T22:40:00Z</t>
+          <t>2026-07-10T01:45:00Z</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -43081,17 +43085,17 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Framber Valdez</t>
+          <t>Carson Whisenhunt</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>664285</t>
+          <t>687931</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -43100,7 +43104,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -43114,26 +43118,26 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P154" t="n">
-        <v>25.4</v>
+        <v>25.9</v>
       </c>
       <c r="Q154" t="n">
-        <v>36.7</v>
+        <v>31.9</v>
       </c>
       <c r="R154" t="n">
-        <v>27.6</v>
+        <v>19.3</v>
       </c>
       <c r="S154" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T154" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U154" t="n">
-        <v>59.1</v>
+        <v>64.8</v>
       </c>
       <c r="V154" t="inlineStr">
         <is>
@@ -43147,7 +43151,7 @@
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y154" t="inlineStr">
@@ -43189,7 +43193,7 @@
       </c>
       <c r="AH154" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI154" t="inlineStr">
@@ -43209,114 +43213,114 @@
       </c>
       <c r="AL154" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.8% barrel, 1.8 HR allowed</t>
         </is>
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>31.63</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
-          <t>97.9399</t>
+          <t>99.7297</t>
         </is>
       </c>
       <c r="AR154" t="inlineStr">
         <is>
-          <t>0.3866</t>
+          <t>0.3649</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>0.1571</t>
+          <t>0.1229</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr">
         <is>
-          <t>0.2963</t>
+          <t>0.3168</t>
         </is>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>29.58</t>
+          <t>23.22</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>0.2058</t>
+          <t>0.1385</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>43.36</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>90.17</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="BD154" t="inlineStr">
         <is>
-          <t>0.3952</t>
+          <t>0.4295</t>
         </is>
       </c>
       <c r="BE154" t="inlineStr">
         <is>
-          <t>0.1444</t>
+          <t>0.1486</t>
         </is>
       </c>
       <c r="BF154" t="inlineStr">
         <is>
-          <t>20.84</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="BG154" t="inlineStr"/>
       <c r="BH154" t="inlineStr"/>
       <c r="BI154" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ154" t="inlineStr"/>
@@ -43327,56 +43331,56 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>641680</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-07-09T17:10:00Z</t>
+          <t>2026-07-09T22:40:00Z</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Paul Blackburn</t>
+          <t>Framber Valdez</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>621112</t>
+          <t>664285</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>42.2</v>
+        <v>42.5</v>
       </c>
       <c r="M155" t="inlineStr">
         <is>
@@ -43390,60 +43394,60 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P155" t="n">
-        <v>41.1</v>
+        <v>25.4</v>
       </c>
       <c r="Q155" t="n">
-        <v>22.4</v>
+        <v>36.7</v>
       </c>
       <c r="R155" t="n">
-        <v>41.1</v>
+        <v>27.6</v>
       </c>
       <c r="S155" t="n">
-        <v>76.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T155" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U155" t="n">
-        <v>37.4</v>
+        <v>59.1</v>
       </c>
       <c r="V155" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W155" t="inlineStr">
+      <c r="Z155" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X155" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>order MLB 6 vs RotoWire 5</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
@@ -43465,12 +43469,12 @@
       </c>
       <c r="AH155" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ155" t="inlineStr">
@@ -43485,7 +43489,7 @@
       </c>
       <c r="AL155" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 3.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM155" t="inlineStr">
@@ -43495,112 +43499,104 @@
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>7.74</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>31.63</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>91.35</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
         <is>
-          <t>102.2367</t>
+          <t>97.9399</t>
         </is>
       </c>
       <c r="AR155" t="inlineStr">
         <is>
-          <t>0.3851</t>
+          <t>0.3866</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>0.1527</t>
+          <t>0.1571</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr">
         <is>
-          <t>0.3069</t>
+          <t>0.2963</t>
         </is>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>75.66</t>
+          <t>69.77</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>55.72</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>22.47</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>24.89</t>
+          <t>29.58</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>0.1372</t>
+          <t>0.2058</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>33.52</t>
+          <t>43.36</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>86.61</t>
+          <t>90.17</t>
         </is>
       </c>
       <c r="BD155" t="inlineStr">
         <is>
-          <t>0.3633</t>
+          <t>0.3952</t>
         </is>
       </c>
       <c r="BE155" t="inlineStr">
         <is>
-          <t>0.1242</t>
+          <t>0.1444</t>
         </is>
       </c>
       <c r="BF155" t="inlineStr">
         <is>
-          <t>21.79</t>
-        </is>
-      </c>
-      <c r="BG155" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH155" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>20.84</t>
+        </is>
+      </c>
+      <c r="BG155" t="inlineStr"/>
+      <c r="BH155" t="inlineStr"/>
       <c r="BI155" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ155" t="inlineStr"/>
@@ -43611,27 +43607,27 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>702332</t>
+          <t>683146</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Caleb Durbin</t>
+          <t>Brett Baty</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-09T18:10:00Z</t>
+          <t>2026-07-09T17:10:00Z</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -43641,26 +43637,26 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>
@@ -43678,22 +43674,22 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>7.3</v>
+        <v>37.6</v>
       </c>
       <c r="Q156" t="n">
-        <v>40.3</v>
+        <v>34.3</v>
       </c>
       <c r="R156" t="n">
-        <v>66.59999999999999</v>
+        <v>44.3</v>
       </c>
       <c r="S156" t="n">
-        <v>86.40000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T156" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U156" t="n">
-        <v>20.8</v>
+        <v>26.4</v>
       </c>
       <c r="V156" t="inlineStr">
         <is>
@@ -43707,7 +43703,7 @@
       </c>
       <c r="X156" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y156" t="inlineStr">
@@ -43717,7 +43713,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -43725,10 +43721,14 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr"/>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>order MLB 9 vs RotoWire 8</t>
+        </is>
+      </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD156" t="inlineStr"/>
@@ -43745,27 +43745,27 @@
       </c>
       <c r="AH156" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 1 HR</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL156" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.6% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AM156" t="inlineStr">
@@ -43775,112 +43775,112 @@
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>84.92</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>96.3013</t>
+          <t>101.0475</t>
         </is>
       </c>
       <c r="AR156" t="inlineStr">
         <is>
-          <t>0.3424</t>
+          <t>0.3912</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.1539</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr">
         <is>
-          <t>0.2938</t>
+          <t>0.3116</t>
         </is>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>51.16</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>0.1527</t>
+          <t>0.1152</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>35.86</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.99</t>
         </is>
       </c>
       <c r="BD156" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.4123</t>
         </is>
       </c>
       <c r="BE156" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>0.1612</t>
         </is>
       </c>
       <c r="BF156" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>26.78</t>
         </is>
       </c>
       <c r="BG156" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH156" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI156" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ156" t="inlineStr"/>
@@ -43891,22 +43891,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>683146</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Brett Baty</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -43921,17 +43921,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Paul Blackburn</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>621112</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -43954,26 +43954,26 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P157" t="n">
-        <v>37.6</v>
+        <v>41.1</v>
       </c>
       <c r="Q157" t="n">
-        <v>34.3</v>
+        <v>22.4</v>
       </c>
       <c r="R157" t="n">
-        <v>44.3</v>
+        <v>41.1</v>
       </c>
       <c r="S157" t="n">
-        <v>44.8</v>
+        <v>76.2</v>
       </c>
       <c r="T157" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U157" t="n">
-        <v>26.4</v>
+        <v>36.7</v>
       </c>
       <c r="V157" t="inlineStr">
         <is>
@@ -43987,7 +43987,7 @@
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
@@ -44007,7 +44007,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>order MLB 9 vs RotoWire 8</t>
+          <t>order MLB 6 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
@@ -44029,27 +44029,27 @@
       </c>
       <c r="AH157" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL157" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.6% barrel, 13.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 3.9 HR allowed</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
@@ -44059,112 +44059,112 @@
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>7.74</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>91.35</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>101.0475</t>
+          <t>102.2367</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
         <is>
-          <t>0.3912</t>
+          <t>0.3851</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>0.1539</t>
+          <t>0.1527</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>0.3116</t>
+          <t>0.3069</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.66</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>51.16</t>
+          <t>55.72</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>22.47</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>24.89</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>0.1152</t>
+          <t>0.1372</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>35.86</t>
+          <t>33.52</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>87.99</t>
+          <t>86.61</t>
         </is>
       </c>
       <c r="BD157" t="inlineStr">
         <is>
-          <t>0.4123</t>
+          <t>0.3633</t>
         </is>
       </c>
       <c r="BE157" t="inlineStr">
         <is>
-          <t>0.1612</t>
+          <t>0.1242</t>
         </is>
       </c>
       <c r="BF157" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="BG157" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH157" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI157" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ157" t="inlineStr"/>
@@ -44480,7 +44480,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -45320,7 +45320,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -51802,7 +51802,7 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ185" t="inlineStr">
@@ -53904,7 +53904,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -56404,7 +56404,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -57272,7 +57272,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="M205" t="inlineStr">
         <is>
@@ -57305,7 +57305,7 @@
         <v>50</v>
       </c>
       <c r="U205" t="n">
-        <v>40.3</v>
+        <v>37.8</v>
       </c>
       <c r="V205" t="inlineStr">
         <is>
@@ -57358,7 +57358,7 @@
       </c>
       <c r="AI205" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ205" t="inlineStr">
@@ -57368,7 +57368,7 @@
       </c>
       <c r="AK205" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/15, 1 HR</t>
+          <t>Last 7 games: 4/16, 1 HR</t>
         </is>
       </c>
       <c r="AL205" t="inlineStr">
@@ -63914,7 +63914,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -64498,7 +64498,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>64.3</v>
+        <v>64.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -64531,7 +64531,7 @@
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>82.7</v>
+        <v>87</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -64583,22 +64583,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -65318,7 +65318,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -65878,7 +65878,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -66158,7 +66158,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -66438,7 +66438,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -68910,7 +68910,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
